--- a/Po_Status.xlsx
+++ b/Po_Status.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1877">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1881">
   <si>
     <t>PO Status</t>
   </si>
@@ -5477,9 +5477,6 @@
     <t>PDNO-1258</t>
   </si>
   <si>
-    <t>F5, F4, F6, F7</t>
-  </si>
-  <si>
     <t>TAPL-A-2794</t>
   </si>
   <si>
@@ -5528,19 +5525,19 @@
     <t>PDNO-1264</t>
   </si>
   <si>
-    <t>F28, F29, F33, P12, F31, F30, P8, F32, F34, P7, F35, P11</t>
+    <t>F28, F29, F33, P12, F31, F30, P8, F32, F34, F35, P7, P11</t>
   </si>
   <si>
     <t>PDNO-1265</t>
   </si>
   <si>
-    <t>F8, F9, F10</t>
+    <t>F8, F10, F9</t>
   </si>
   <si>
     <t>PDNO-1266</t>
   </si>
   <si>
-    <t>A, C, D, E, B</t>
+    <t>A, C, E, B, D</t>
   </si>
   <si>
     <t>SAN 75D 72F SIM FD 1H, DB900083IK</t>
@@ -5588,7 +5585,7 @@
     <t>PDNO-1273</t>
   </si>
   <si>
-    <t>L6, L, J, K, L5, L8, L7, L4</t>
+    <t>L6, L, J, K, L5, L8, L4, L7</t>
   </si>
   <si>
     <t>SHENGHONG 90DTEX 144F CD SD, X856/M010</t>
@@ -5627,13 +5624,13 @@
     <t>WARPSTREME-ALPHA-218INCH-28GG</t>
   </si>
   <si>
-    <t>KM05, KM04, KM03</t>
+    <t>KM03, KM04, KM05</t>
   </si>
   <si>
     <t>PDNO-1278</t>
   </si>
   <si>
-    <t>L9, L10, L13, L11, L15, L14, L12, L16</t>
+    <t>L9, L10, L11, L15, L13, L14, L12, L16</t>
   </si>
   <si>
     <t>SHENGHONG 55DTEX 48F PBT BEY SD, J350/N300</t>
@@ -5645,7 +5642,22 @@
     <t>PDNO-1279</t>
   </si>
   <si>
-    <t>Grand Summary(764) - Sum</t>
+    <t>PDNO-1280</t>
+  </si>
+  <si>
+    <t>Not Scheduled</t>
+  </si>
+  <si>
+    <t>PDNO-1281</t>
+  </si>
+  <si>
+    <t>TAPL-A-2449-A</t>
+  </si>
+  <si>
+    <t>PDNO-1282</t>
+  </si>
+  <si>
+    <t>Grand Summary(767) - Sum</t>
   </si>
 </sst>
 </file>
@@ -6034,7 +6046,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:W766"/>
+  <dimension ref="A1:W769"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="29.421387" bestFit="true" customWidth="true" style="0"/>
@@ -55001,13 +55013,13 @@
         <v>671</v>
       </c>
       <c r="G690" s="5">
-        <v>627</v>
+        <v>640</v>
       </c>
       <c r="H690" s="6">
         <v>15382.982</v>
       </c>
       <c r="I690" s="6">
-        <v>15760.66</v>
+        <v>16088.32</v>
       </c>
       <c r="J690" s="7">
         <v>0</v>
@@ -55708,16 +55720,16 @@
         <v>1719</v>
       </c>
       <c r="F700" s="5">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="G700" s="5">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="H700" s="6">
         <v>13159.359</v>
       </c>
       <c r="I700" s="6">
-        <v>12823.2</v>
+        <v>12899.02</v>
       </c>
       <c r="J700" s="7">
         <v>0</v>
@@ -56705,13 +56717,13 @@
         <v>121</v>
       </c>
       <c r="G714" s="5">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="H714" s="6">
         <v>3860.236</v>
       </c>
       <c r="I714" s="6">
-        <v>2245.62</v>
+        <v>2498.32</v>
       </c>
       <c r="J714" s="7">
         <v>0</v>
@@ -56989,13 +57001,13 @@
         <v>300</v>
       </c>
       <c r="G718" s="5">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="H718" s="6">
         <v>6220.87</v>
       </c>
       <c r="I718" s="6">
-        <v>5065.68</v>
+        <v>5238.22</v>
       </c>
       <c r="J718" s="7">
         <v>0</v>
@@ -57486,13 +57498,13 @@
         <v>192</v>
       </c>
       <c r="G725" s="5">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H725" s="6">
         <v>2770.005</v>
       </c>
       <c r="I725" s="6">
-        <v>2458.82</v>
+        <v>2533.88</v>
       </c>
       <c r="J725" s="7">
         <v>0</v>
@@ -57625,16 +57637,16 @@
         <v>919</v>
       </c>
       <c r="F727" s="5">
-        <v>200</v>
+        <v>114</v>
       </c>
       <c r="G727" s="5">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H727" s="6">
         <v>2518</v>
       </c>
       <c r="I727" s="6">
-        <v>2664</v>
+        <v>2813.48</v>
       </c>
       <c r="J727" s="7">
         <v>0</v>
@@ -57983,13 +57995,13 @@
         <v>200</v>
       </c>
       <c r="G732" s="5">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H732" s="6">
         <v>3672.787</v>
       </c>
       <c r="I732" s="6">
-        <v>4034.18</v>
+        <v>4214.42</v>
       </c>
       <c r="J732" s="7">
         <v>0</v>
@@ -58054,13 +58066,13 @@
         <v>288</v>
       </c>
       <c r="G733" s="5">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="H733" s="6">
         <v>5163.44</v>
       </c>
       <c r="I733" s="6">
-        <v>4759.86</v>
+        <v>5009.92</v>
       </c>
       <c r="J733" s="7">
         <v>0</v>
@@ -58196,13 +58208,13 @@
         <v>91</v>
       </c>
       <c r="G735" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H735" s="6">
         <v>1359.6</v>
       </c>
       <c r="I735" s="6">
-        <v>651.54</v>
+        <v>701.5</v>
       </c>
       <c r="J735" s="7">
         <v>0</v>
@@ -58829,19 +58841,19 @@
         <v>1655</v>
       </c>
       <c r="E744" s="4" t="s">
-        <v>1820</v>
+        <v>745</v>
       </c>
       <c r="F744" s="5">
         <v>512</v>
       </c>
       <c r="G744" s="5">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="H744" s="6">
         <v>10589.6</v>
       </c>
       <c r="I744" s="6">
-        <v>9835.3</v>
+        <v>10587.66</v>
       </c>
       <c r="J744" s="7">
         <v>0</v>
@@ -58891,10 +58903,10 @@
         <v>1629</v>
       </c>
       <c r="B745" s="3" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C745" s="3" t="s">
         <v>1821</v>
-      </c>
-      <c r="C745" s="3" t="s">
-        <v>1822</v>
       </c>
       <c r="D745" s="3" t="s">
         <v>852</v>
@@ -58906,13 +58918,13 @@
         <v>200</v>
       </c>
       <c r="G745" s="5">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="H745" s="6">
         <v>1904</v>
       </c>
       <c r="I745" s="6">
-        <v>1548.48</v>
+        <v>1874.4</v>
       </c>
       <c r="J745" s="7">
         <v>0</v>
@@ -58962,28 +58974,28 @@
         <v>1629</v>
       </c>
       <c r="B746" s="3" t="s">
+        <v>1822</v>
+      </c>
+      <c r="C746" s="3" t="s">
         <v>1823</v>
-      </c>
-      <c r="C746" s="3" t="s">
-        <v>1824</v>
       </c>
       <c r="D746" s="3" t="s">
         <v>1520</v>
       </c>
       <c r="E746" s="4" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="F746" s="5">
         <v>800</v>
       </c>
       <c r="G746" s="5">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="H746" s="6">
         <v>10673.024</v>
       </c>
       <c r="I746" s="6">
-        <v>9258.62</v>
+        <v>9506.2</v>
       </c>
       <c r="J746" s="7">
         <v>0</v>
@@ -59033,28 +59045,28 @@
         <v>1629</v>
       </c>
       <c r="B747" s="3" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C747" s="3" t="s">
         <v>1826</v>
-      </c>
-      <c r="C747" s="3" t="s">
-        <v>1827</v>
       </c>
       <c r="D747" s="3" t="s">
         <v>101</v>
       </c>
       <c r="E747" s="4" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="F747" s="5">
         <v>300</v>
       </c>
       <c r="G747" s="5">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H747" s="6">
         <v>1847.79</v>
       </c>
       <c r="I747" s="6">
-        <v>521.4</v>
+        <v>645.62</v>
       </c>
       <c r="J747" s="7">
         <v>0</v>
@@ -59104,28 +59116,28 @@
         <v>1629</v>
       </c>
       <c r="B748" s="3" t="s">
+        <v>1828</v>
+      </c>
+      <c r="C748" s="3" t="s">
         <v>1829</v>
       </c>
-      <c r="C748" s="3" t="s">
+      <c r="D748" s="3" t="s">
         <v>1830</v>
       </c>
-      <c r="D748" s="3" t="s">
-        <v>1831</v>
-      </c>
       <c r="E748" s="4" t="s">
-        <v>321</v>
+        <v>183</v>
       </c>
       <c r="F748" s="5">
         <v>100</v>
       </c>
       <c r="G748" s="5">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H748" s="6">
         <v>2462.4</v>
       </c>
       <c r="I748" s="6">
-        <v>1956.78</v>
+        <v>2132.44</v>
       </c>
       <c r="J748" s="7">
         <v>0</v>
@@ -59175,28 +59187,28 @@
         <v>1629</v>
       </c>
       <c r="B749" s="3" t="s">
+        <v>1831</v>
+      </c>
+      <c r="C749" s="3" t="s">
         <v>1832</v>
-      </c>
-      <c r="C749" s="3" t="s">
-        <v>1833</v>
       </c>
       <c r="D749" s="3" t="s">
         <v>221</v>
       </c>
       <c r="E749" s="4" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="F749" s="5">
         <v>50</v>
       </c>
       <c r="G749" s="5">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H749" s="6">
         <v>835.2</v>
       </c>
       <c r="I749" s="6">
-        <v>857.88</v>
+        <v>931.94</v>
       </c>
       <c r="J749" s="7">
         <v>0</v>
@@ -59246,28 +59258,28 @@
         <v>1629</v>
       </c>
       <c r="B750" s="3" t="s">
+        <v>1834</v>
+      </c>
+      <c r="C750" s="3" t="s">
         <v>1835</v>
-      </c>
-      <c r="C750" s="3" t="s">
-        <v>1836</v>
       </c>
       <c r="D750" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E750" s="4" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="F750" s="5">
         <v>600</v>
       </c>
       <c r="G750" s="5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H750" s="6">
         <v>7202.874</v>
       </c>
       <c r="I750" s="6">
-        <v>853.5</v>
+        <v>878.58</v>
       </c>
       <c r="J750" s="7">
         <v>0</v>
@@ -59320,25 +59332,25 @@
         <v>1745</v>
       </c>
       <c r="C751" s="3" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="D751" s="3" t="s">
         <v>834</v>
       </c>
       <c r="E751" s="4" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="F751" s="5">
         <v>150</v>
       </c>
       <c r="G751" s="5">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H751" s="6">
         <v>2526.3</v>
       </c>
       <c r="I751" s="6">
-        <v>1837.04</v>
+        <v>2063.04</v>
       </c>
       <c r="J751" s="7">
         <v>0</v>
@@ -59391,25 +59403,25 @@
         <v>1650</v>
       </c>
       <c r="C752" s="3" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="D752" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E752" s="4" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="F752" s="5">
         <v>400</v>
       </c>
       <c r="G752" s="5">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="H752" s="6">
         <v>5469.582</v>
       </c>
       <c r="I752" s="6">
-        <v>2720.18</v>
+        <v>3092.74</v>
       </c>
       <c r="J752" s="7">
         <v>0</v>
@@ -59445,7 +59457,7 @@
         <v>997</v>
       </c>
       <c r="U752" s="3" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="V752" s="3" t="s">
         <v>29</v>
@@ -59462,7 +59474,7 @@
         <v>1648</v>
       </c>
       <c r="C753" s="3" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="D753" s="3" t="s">
         <v>44</v>
@@ -59474,13 +59486,13 @@
         <v>100</v>
       </c>
       <c r="G753" s="5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H753" s="6">
         <v>1379.6</v>
       </c>
       <c r="I753" s="6">
-        <v>749.22</v>
+        <v>799.1</v>
       </c>
       <c r="J753" s="7">
         <v>0</v>
@@ -59533,25 +59545,25 @@
         <v>1805</v>
       </c>
       <c r="C754" s="3" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="D754" s="3" t="s">
         <v>1404</v>
       </c>
       <c r="E754" s="4" t="s">
-        <v>1171</v>
+        <v>1557</v>
       </c>
       <c r="F754" s="5">
         <v>64</v>
       </c>
       <c r="G754" s="5">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H754" s="6">
         <v>1049.4</v>
       </c>
       <c r="I754" s="6">
-        <v>776.16</v>
+        <v>902.36</v>
       </c>
       <c r="J754" s="7">
         <v>0</v>
@@ -59601,10 +59613,10 @@
         <v>1629</v>
       </c>
       <c r="B755" s="3" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C755" s="3" t="s">
         <v>1845</v>
-      </c>
-      <c r="C755" s="3" t="s">
-        <v>1846</v>
       </c>
       <c r="D755" s="3" t="s">
         <v>1215</v>
@@ -59672,10 +59684,10 @@
         <v>1629</v>
       </c>
       <c r="B756" s="3" t="s">
+        <v>1846</v>
+      </c>
+      <c r="C756" s="3" t="s">
         <v>1847</v>
-      </c>
-      <c r="C756" s="3" t="s">
-        <v>1848</v>
       </c>
       <c r="D756" s="3" t="s">
         <v>210</v>
@@ -59687,13 +59699,13 @@
         <v>64</v>
       </c>
       <c r="G756" s="5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H756" s="6">
         <v>1083.061</v>
       </c>
       <c r="I756" s="6">
-        <v>502.22</v>
+        <v>552.6</v>
       </c>
       <c r="J756" s="7">
         <v>0</v>
@@ -59743,16 +59755,16 @@
         <v>1629</v>
       </c>
       <c r="B757" s="3" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C757" s="3" t="s">
         <v>1849</v>
-      </c>
-      <c r="C757" s="3" t="s">
-        <v>1850</v>
       </c>
       <c r="D757" s="3" t="s">
         <v>1785</v>
       </c>
       <c r="E757" s="4" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="F757" s="5">
         <v>100</v>
@@ -59814,16 +59826,16 @@
         <v>1629</v>
       </c>
       <c r="B758" s="3" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C758" s="3" t="s">
         <v>1852</v>
-      </c>
-      <c r="C758" s="3" t="s">
-        <v>1853</v>
       </c>
       <c r="D758" s="3" t="s">
         <v>1803</v>
       </c>
       <c r="E758" s="4" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="F758" s="5">
         <v>100</v>
@@ -59885,28 +59897,28 @@
         <v>1629</v>
       </c>
       <c r="B759" s="3" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C759" s="3" t="s">
         <v>1855</v>
-      </c>
-      <c r="C759" s="3" t="s">
-        <v>1856</v>
       </c>
       <c r="D759" s="3" t="s">
         <v>1608</v>
       </c>
       <c r="E759" s="4" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="F759" s="5">
         <v>400</v>
       </c>
       <c r="G759" s="5">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="H759" s="6">
         <v>5020.731</v>
       </c>
       <c r="I759" s="6">
-        <v>1003.26</v>
+        <v>1651.68</v>
       </c>
       <c r="J759" s="7">
         <v>0</v>
@@ -59939,7 +59951,7 @@
         <v>0</v>
       </c>
       <c r="T759" s="3" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="U759" s="3" t="s">
         <v>750</v>
@@ -59959,25 +59971,25 @@
         <v>1816</v>
       </c>
       <c r="C760" s="3" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="D760" s="3" t="s">
         <v>1404</v>
       </c>
       <c r="E760" s="4" t="s">
-        <v>1174</v>
+        <v>1582</v>
       </c>
       <c r="F760" s="5">
         <v>52</v>
       </c>
       <c r="G760" s="5">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H760" s="6">
         <v>896.4</v>
       </c>
       <c r="I760" s="6">
-        <v>275.04</v>
+        <v>374.78</v>
       </c>
       <c r="J760" s="7">
         <v>0</v>
@@ -60027,28 +60039,28 @@
         <v>1629</v>
       </c>
       <c r="B761" s="3" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C761" s="3" t="s">
         <v>1860</v>
       </c>
-      <c r="C761" s="3" t="s">
+      <c r="D761" s="3" t="s">
         <v>1861</v>
       </c>
-      <c r="D761" s="3" t="s">
+      <c r="E761" s="4" t="s">
         <v>1862</v>
-      </c>
-      <c r="E761" s="4" t="s">
-        <v>1863</v>
       </c>
       <c r="F761" s="5">
         <v>100</v>
       </c>
       <c r="G761" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H761" s="6">
         <v>1784</v>
       </c>
       <c r="I761" s="6">
-        <v>100</v>
+        <v>151.48</v>
       </c>
       <c r="J761" s="7">
         <v>0</v>
@@ -60084,7 +60096,7 @@
         <v>1757</v>
       </c>
       <c r="U761" s="3" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="V761" s="3" t="s">
         <v>29</v>
@@ -60098,28 +60110,28 @@
         <v>1629</v>
       </c>
       <c r="B762" s="3" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C762" s="3" t="s">
         <v>1865</v>
-      </c>
-      <c r="C762" s="3" t="s">
-        <v>1866</v>
       </c>
       <c r="D762" s="3" t="s">
         <v>1507</v>
       </c>
       <c r="E762" s="4" t="s">
-        <v>904</v>
+        <v>956</v>
       </c>
       <c r="F762" s="5">
         <v>300</v>
       </c>
       <c r="G762" s="5">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="H762" s="6">
         <v>0</v>
       </c>
       <c r="I762" s="6">
-        <v>2139.18</v>
+        <v>3342.44</v>
       </c>
       <c r="J762" s="7">
         <v>0</v>
@@ -60169,28 +60181,28 @@
         <v>1629</v>
       </c>
       <c r="B763" s="3" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C763" s="3" t="s">
         <v>1867</v>
       </c>
-      <c r="C763" s="3" t="s">
+      <c r="D763" s="3" t="s">
         <v>1868</v>
       </c>
-      <c r="D763" s="3" t="s">
+      <c r="E763" s="4" t="s">
         <v>1869</v>
       </c>
-      <c r="E763" s="4" t="s">
-        <v>1870</v>
-      </c>
       <c r="F763" s="5">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="G763" s="5">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H763" s="6">
-        <v>1114.26</v>
+        <v>1744.84</v>
       </c>
       <c r="I763" s="6">
-        <v>1505.52</v>
+        <v>1744.84</v>
       </c>
       <c r="J763" s="7">
         <v>0</v>
@@ -60199,13 +60211,13 @@
         <v>0</v>
       </c>
       <c r="L763" s="9">
-        <v>459.55</v>
+        <v>719.6</v>
       </c>
       <c r="M763" s="8">
         <v>0</v>
       </c>
       <c r="N763" s="9">
-        <v>654.71</v>
+        <v>1025.24</v>
       </c>
       <c r="O763" s="8">
         <v>0</v>
@@ -60243,23 +60255,25 @@
         <v>1809</v>
       </c>
       <c r="C764" s="3" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="D764" s="3" t="s">
         <v>1811</v>
       </c>
       <c r="E764" s="4" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="F764" s="5">
         <v>400</v>
       </c>
-      <c r="G764" s="5"/>
+      <c r="G764" s="5">
+        <v>20</v>
+      </c>
       <c r="H764" s="6">
         <v>2097.5</v>
       </c>
       <c r="I764" s="6">
-        <v>0</v>
+        <v>499.8</v>
       </c>
       <c r="J764" s="7">
         <v>0</v>
@@ -60298,7 +60312,7 @@
         <v>750</v>
       </c>
       <c r="V764" s="3" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="W764" s="3" t="s">
         <v>29</v>
@@ -60306,13 +60320,13 @@
     </row>
     <row r="765" spans="1:23">
       <c r="A765" s="3" t="s">
-        <v>1629</v>
+        <v>23</v>
       </c>
       <c r="B765" s="3" t="s">
+        <v>1873</v>
+      </c>
+      <c r="C765" s="3" t="s">
         <v>1874</v>
-      </c>
-      <c r="C765" s="3" t="s">
-        <v>1875</v>
       </c>
       <c r="D765" s="3" t="s">
         <v>1800</v>
@@ -60327,7 +60341,7 @@
         <v>1</v>
       </c>
       <c r="H765" s="6">
-        <v>0</v>
+        <v>29.9</v>
       </c>
       <c r="I765" s="6">
         <v>29.9</v>
@@ -60339,16 +60353,16 @@
         <v>0</v>
       </c>
       <c r="L765" s="9">
-        <v>0</v>
+        <v>17.39</v>
       </c>
       <c r="M765" s="8">
-        <v>0</v>
+        <v>58.16</v>
       </c>
       <c r="N765" s="9">
-        <v>0</v>
+        <v>12.51</v>
       </c>
       <c r="O765" s="8">
-        <v>0</v>
+        <v>41.84</v>
       </c>
       <c r="P765" s="9">
         <v>0</v>
@@ -60376,34 +60390,243 @@
       </c>
     </row>
     <row r="766" spans="1:23">
-      <c r="A766" s="1" t="s">
+      <c r="A766" s="3" t="s">
+        <v>1629</v>
+      </c>
+      <c r="B766" s="3" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C766" s="3" t="s">
+        <v>1875</v>
+      </c>
+      <c r="D766" s="3" t="s">
+        <v>1868</v>
+      </c>
+      <c r="E766" s="4" t="s">
+        <v>1686</v>
+      </c>
+      <c r="F766" s="5">
+        <v>100</v>
+      </c>
+      <c r="G766" s="5">
+        <v>16</v>
+      </c>
+      <c r="H766" s="6">
+        <v>0</v>
+      </c>
+      <c r="I766" s="6">
+        <v>478.98</v>
+      </c>
+      <c r="J766" s="7">
+        <v>0</v>
+      </c>
+      <c r="K766" s="8">
+        <v>0</v>
+      </c>
+      <c r="L766" s="9">
+        <v>0</v>
+      </c>
+      <c r="M766" s="8">
+        <v>0</v>
+      </c>
+      <c r="N766" s="9">
+        <v>0</v>
+      </c>
+      <c r="O766" s="8">
+        <v>0</v>
+      </c>
+      <c r="P766" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q766" s="8">
+        <v>0</v>
+      </c>
+      <c r="R766" s="9">
+        <v>0</v>
+      </c>
+      <c r="S766" s="8">
+        <v>0</v>
+      </c>
+      <c r="T766" s="3" t="s">
+        <v>1757</v>
+      </c>
+      <c r="U766" s="3" t="s">
+        <v>1872</v>
+      </c>
+      <c r="V766" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="W766" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="767" spans="1:23">
+      <c r="A767" s="3" t="s">
         <v>1876</v>
       </c>
-      <c r="F766" s="10">
-        <v>184307</v>
-      </c>
-      <c r="G766" s="10">
-        <v>178414</v>
-      </c>
-      <c r="H766" s="11">
-        <v>4650369.189</v>
-      </c>
-      <c r="I766" s="11">
-        <v>4609886.539</v>
-      </c>
-      <c r="J766" s="12">
+      <c r="B767" s="3" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C767" s="3" t="s">
+        <v>1877</v>
+      </c>
+      <c r="D767" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="E767" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F767" s="5">
+        <v>119</v>
+      </c>
+      <c r="G767" s="5"/>
+      <c r="H767" s="6">
+        <v>0</v>
+      </c>
+      <c r="I767" s="6">
+        <v>0</v>
+      </c>
+      <c r="J767" s="7">
+        <v>0</v>
+      </c>
+      <c r="K767" s="8">
+        <v>0</v>
+      </c>
+      <c r="L767" s="9">
+        <v>0</v>
+      </c>
+      <c r="M767" s="8">
+        <v>0</v>
+      </c>
+      <c r="N767" s="9">
+        <v>0</v>
+      </c>
+      <c r="O767" s="8">
+        <v>0</v>
+      </c>
+      <c r="P767" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q767" s="8">
+        <v>0</v>
+      </c>
+      <c r="R767" s="9">
+        <v>0</v>
+      </c>
+      <c r="S767" s="8">
+        <v>0</v>
+      </c>
+      <c r="T767" s="3" t="s">
+        <v>1749</v>
+      </c>
+      <c r="U767" s="3" t="s">
+        <v>1872</v>
+      </c>
+      <c r="V767" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="W767" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="768" spans="1:23">
+      <c r="A768" s="3" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B768" s="3" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C768" s="3" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D768" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E768" s="4" t="s">
+        <v>1688</v>
+      </c>
+      <c r="F768" s="5">
+        <v>1</v>
+      </c>
+      <c r="G768" s="5"/>
+      <c r="H768" s="6">
+        <v>0</v>
+      </c>
+      <c r="I768" s="6">
+        <v>0</v>
+      </c>
+      <c r="J768" s="7">
+        <v>0</v>
+      </c>
+      <c r="K768" s="8">
+        <v>0</v>
+      </c>
+      <c r="L768" s="9">
+        <v>0</v>
+      </c>
+      <c r="M768" s="8">
+        <v>0</v>
+      </c>
+      <c r="N768" s="9">
+        <v>0</v>
+      </c>
+      <c r="O768" s="8">
+        <v>0</v>
+      </c>
+      <c r="P768" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q768" s="8">
+        <v>0</v>
+      </c>
+      <c r="R768" s="9">
+        <v>0</v>
+      </c>
+      <c r="S768" s="8">
+        <v>0</v>
+      </c>
+      <c r="T768" s="3" t="s">
+        <v>1644</v>
+      </c>
+      <c r="U768" s="3" t="s">
+        <v>1445</v>
+      </c>
+      <c r="V768" s="3" t="s">
+        <v>1633</v>
+      </c>
+      <c r="W768" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="769" spans="1:23">
+      <c r="A769" s="1" t="s">
+        <v>1880</v>
+      </c>
+      <c r="F769" s="10">
+        <v>184413</v>
+      </c>
+      <c r="G769" s="10">
+        <v>178693</v>
+      </c>
+      <c r="H769" s="11">
+        <v>4651029.669</v>
+      </c>
+      <c r="I769" s="11">
+        <v>4617215.999</v>
+      </c>
+      <c r="J769" s="12">
         <v>618.966</v>
       </c>
-      <c r="L766" s="13">
-        <v>2893186.827</v>
-      </c>
-      <c r="N766" s="13">
-        <v>1625985</v>
-      </c>
-      <c r="P766" s="13">
+      <c r="L769" s="13">
+        <v>2893464.267</v>
+      </c>
+      <c r="N769" s="13">
+        <v>1626368.04</v>
+      </c>
+      <c r="P769" s="13">
         <v>120454.692</v>
       </c>
-      <c r="R766" s="13">
+      <c r="R769" s="13">
         <v>10742.67</v>
       </c>
     </row>
